--- a/Hoadon/HD2026/HDRa/6/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDRa/6/3502550210_HDDienTuMayTinhTien.xlsx
@@ -3194,6 +3194,2626 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H51" s="7"/>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13" t="n">
+        <v>1.6973038E7</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>1546933.0</v>
+      </c>
+      <c r="N51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O51" s="13" t="n">
+        <v>1.8519971E7</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H52" s="7"/>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="13" t="n">
+        <v>4453746.0</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>356300.0</v>
+      </c>
+      <c r="N52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O52" s="13" t="n">
+        <v>4810046.0</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H53" s="7"/>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="13" t="n">
+        <v>1.160973E7</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>1160973.0</v>
+      </c>
+      <c r="N53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>1.2770703E7</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H54" s="7"/>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="13" t="n">
+        <v>7257776.0</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>642258.0</v>
+      </c>
+      <c r="N54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="13" t="n">
+        <v>7900034.0</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H55" s="7"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K55" s="6"/>
+      <c r="L55" s="13" t="n">
+        <v>1.854627E7</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>1843701.0</v>
+      </c>
+      <c r="N55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O55" s="13" t="n">
+        <v>2.0389971E7</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H56" s="7"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K56" s="6"/>
+      <c r="L56" s="13" t="n">
+        <v>6554186.0</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>618880.0</v>
+      </c>
+      <c r="N56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O56" s="13" t="n">
+        <v>7173066.0</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H57" s="7"/>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="13" t="n">
+        <v>1.284609E7</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>1284609.0</v>
+      </c>
+      <c r="N57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>1.4130699E7</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H58" s="7"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K58" s="6"/>
+      <c r="L58" s="13" t="n">
+        <v>1.5515154E7</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>1518849.0</v>
+      </c>
+      <c r="N58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O58" s="13" t="n">
+        <v>1.7034003E7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K59" s="6"/>
+      <c r="L59" s="13" t="n">
+        <v>9295566.0</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>885853.0</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>1.0181419E7</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H60" s="7"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K60" s="6"/>
+      <c r="L60" s="13" t="n">
+        <v>5440222.0</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>529763.0</v>
+      </c>
+      <c r="N60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O60" s="13" t="n">
+        <v>5969985.0</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K61" s="6"/>
+      <c r="L61" s="13" t="n">
+        <v>5440222.0</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>529763.0</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>5969985.0</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H62" s="7"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K62" s="6"/>
+      <c r="L62" s="13" t="n">
+        <v>9179808.0</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>870203.0</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>1.0050011E7</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H63" s="7"/>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="13" t="n">
+        <v>1.201281E7</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>1201281.0</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>1.3214091E7</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K64" s="6"/>
+      <c r="L64" s="13" t="n">
+        <v>1533665.0</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>146330.0</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>1679995.0</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H65" s="7"/>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="13" t="n">
+        <v>3767528.0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>342493.0</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>4110021.0</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H66" s="7"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K66" s="6"/>
+      <c r="L66" s="13" t="n">
+        <v>1.372806E7</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>1372806.0</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>1.5100866E7</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H67" s="7"/>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="13" t="n">
+        <v>4905619.0</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>392449.0</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>5298068.0</v>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H68" s="7"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K68" s="6"/>
+      <c r="L68" s="13" t="n">
+        <v>6249995.0</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>619999.0</v>
+      </c>
+      <c r="N68" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O68" s="13" t="n">
+        <v>6869994.0</v>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H69" s="7"/>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="13" t="n">
+        <v>3767528.0</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>342493.0</v>
+      </c>
+      <c r="N69" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O69" s="13" t="n">
+        <v>4110021.0</v>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H70" s="7"/>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="13" t="n">
+        <v>1.160973E7</v>
+      </c>
+      <c r="M70" s="13" t="n">
+        <v>1160973.0</v>
+      </c>
+      <c r="N70" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O70" s="13" t="n">
+        <v>1.2770703E7</v>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H71" s="7"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K71" s="6"/>
+      <c r="L71" s="13" t="n">
+        <v>5620778.0</v>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>544207.0</v>
+      </c>
+      <c r="N71" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>6164985.0</v>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H72" s="7"/>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="13" t="n">
+        <v>4453746.0</v>
+      </c>
+      <c r="M72" s="13" t="n">
+        <v>356300.0</v>
+      </c>
+      <c r="N72" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O72" s="13" t="n">
+        <v>4810046.0</v>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H73" s="7"/>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="13" t="n">
+        <v>1.160973E7</v>
+      </c>
+      <c r="M73" s="13" t="n">
+        <v>1160973.0</v>
+      </c>
+      <c r="N73" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>1.2770703E7</v>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H74" s="7"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K74" s="6"/>
+      <c r="L74" s="13" t="n">
+        <v>8.45456E7</v>
+      </c>
+      <c r="M74" s="13" t="n">
+        <v>8454560.0</v>
+      </c>
+      <c r="N74" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O74" s="13" t="n">
+        <v>9.300016E7</v>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H75" s="7"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K75" s="6"/>
+      <c r="L75" s="13" t="n">
+        <v>7803852.0</v>
+      </c>
+      <c r="M75" s="13" t="n">
+        <v>766126.0</v>
+      </c>
+      <c r="N75" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O75" s="13" t="n">
+        <v>8569978.0</v>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>031090024789</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH NGUYỄN VIỆT HÙNG</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>3 đường Trần Huy Liệu, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K76" s="6"/>
+      <c r="L76" s="13" t="n">
+        <v>2621626.0</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>253367.0</v>
+      </c>
+      <c r="N76" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O76" s="13" t="n">
+        <v>2874993.0</v>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H77" s="7"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K77" s="6"/>
+      <c r="L77" s="13" t="n">
+        <v>1.931815E8</v>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>1.931815E7</v>
+      </c>
+      <c r="N77" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O77" s="13" t="n">
+        <v>2.1249965E8</v>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>72.0</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H78" s="7"/>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="13" t="n">
+        <v>4094416.0</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>341553.0</v>
+      </c>
+      <c r="N78" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O78" s="13" t="n">
+        <v>4435969.0</v>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>73.0</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H79" s="7"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K79" s="6"/>
+      <c r="L79" s="13" t="n">
+        <v>2.690925E7</v>
+      </c>
+      <c r="M79" s="13" t="n">
+        <v>2690925.0</v>
+      </c>
+      <c r="N79" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O79" s="13" t="n">
+        <v>2.9600175E7</v>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H80" s="7"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K80" s="6"/>
+      <c r="L80" s="13" t="n">
+        <v>1.6389E7</v>
+      </c>
+      <c r="M80" s="13" t="n">
+        <v>1311120.0</v>
+      </c>
+      <c r="N80" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O80" s="13" t="n">
+        <v>1.770012E7</v>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H81" s="7"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K81" s="6"/>
+      <c r="L81" s="13" t="n">
+        <v>7.09089E7</v>
+      </c>
+      <c r="M81" s="13" t="n">
+        <v>7090890.0</v>
+      </c>
+      <c r="N81" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O81" s="13" t="n">
+        <v>7.799979E7</v>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>077088009229</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH TÂM NGUYỄN (DƯƠNG THẾ HUY)</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>04 đường Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K82" s="6"/>
+      <c r="L82" s="13" t="n">
+        <v>4.2838972E7</v>
+      </c>
+      <c r="M82" s="13" t="n">
+        <v>3828633.0</v>
+      </c>
+      <c r="N82" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O82" s="13" t="n">
+        <v>4.6667605E7</v>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>77.0</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H83" s="7"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K83" s="6"/>
+      <c r="L83" s="13" t="n">
+        <v>6468004.0</v>
+      </c>
+      <c r="M83" s="13" t="n">
+        <v>611986.0</v>
+      </c>
+      <c r="N83" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O83" s="13" t="n">
+        <v>7079990.0</v>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>78.0</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H84" s="7"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K84" s="6"/>
+      <c r="L84" s="13" t="n">
+        <v>2875924.0</v>
+      </c>
+      <c r="M84" s="13" t="n">
+        <v>248148.0</v>
+      </c>
+      <c r="N84" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O84" s="13" t="n">
+        <v>3124072.0</v>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H85" s="7"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K85" s="6"/>
+      <c r="L85" s="13" t="n">
+        <v>5620778.0</v>
+      </c>
+      <c r="M85" s="13" t="n">
+        <v>544207.0</v>
+      </c>
+      <c r="N85" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>6164985.0</v>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H86" s="7"/>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="13" t="n">
+        <v>4083376.0</v>
+      </c>
+      <c r="M86" s="13" t="n">
+        <v>326670.0</v>
+      </c>
+      <c r="N86" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O86" s="13" t="n">
+        <v>4410046.0</v>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H87" s="7"/>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="13" t="n">
+        <v>8215895.0</v>
+      </c>
+      <c r="M87" s="13" t="n">
+        <v>758090.0</v>
+      </c>
+      <c r="N87" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O87" s="13" t="n">
+        <v>8973985.0</v>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>086183017090</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH NGUYỄN THỊ KIM ÁNH</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>137 đường Hoàng Hoa Thám, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K88" s="6"/>
+      <c r="L88" s="13" t="n">
+        <v>3545338.0</v>
+      </c>
+      <c r="M88" s="13" t="n">
+        <v>320681.0</v>
+      </c>
+      <c r="N88" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O88" s="13" t="n">
+        <v>3866019.0</v>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H89" s="7"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="13" t="n">
+        <v>7.5E7</v>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>7500000.0</v>
+      </c>
+      <c r="N89" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O89" s="13" t="n">
+        <v>8.25E7</v>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>84.0</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H90" s="7"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K90" s="6"/>
+      <c r="L90" s="13" t="n">
+        <v>8.72979E7</v>
+      </c>
+      <c r="M90" s="13" t="n">
+        <v>8402010.0</v>
+      </c>
+      <c r="N90" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O90" s="13" t="n">
+        <v>9.569991E7</v>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
